--- a/public/exports-from-60/29189455.xlsx
+++ b/public/exports-from-60/29189455.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 28A</t>
+          <t xml:space="preserve">Døstrupvej 1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600946</t>
+          <t xml:space="preserve">3346368</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="J133">
-        <v>1095</v>
+        <v>506</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311188283</t>
+          <t xml:space="preserve">311189004</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-06</t>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30A</t>
+          <t xml:space="preserve">Døstrupvej 1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,20 +10026,20 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601054</t>
+          <t xml:space="preserve">3346368</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J134">
-        <v>400</v>
+        <v>824</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311188287</t>
+          <t xml:space="preserve">311189007</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-06</t>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 1</t>
+          <t xml:space="preserve">Døstrupvej 3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10106,15 +10106,15 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J135">
-        <v>506</v>
+        <v>228</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189004</t>
+          <t xml:space="preserve">311189034</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 1</t>
+          <t xml:space="preserve">Døstrupvej 3A</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,20 +10176,20 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346368</t>
+          <t xml:space="preserve">751530, 3346372</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J136">
-        <v>824</v>
+        <v>1064</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189007</t>
+          <t xml:space="preserve">311189044</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3</t>
+          <t xml:space="preserve">Døstrupvej 3A</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346368</t>
+          <t xml:space="preserve">751530, 3346372</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J137">
-        <v>228</v>
+        <v>667</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189034</t>
+          <t xml:space="preserve">311189044</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,30 +10316,30 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3A</t>
+          <t xml:space="preserve">Vikingvej 2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">751530, 3346372</t>
+          <t xml:space="preserve">3339443</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J138">
-        <v>1064</v>
+        <v>206</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189044</t>
+          <t xml:space="preserve">311190150</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-08</t>
+          <t xml:space="preserve">2026-07-14</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,30 +10391,30 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3A</t>
+          <t xml:space="preserve">Vikingvej 4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">751530, 3346372</t>
+          <t xml:space="preserve">3339443</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J139">
-        <v>667</v>
+        <v>5980</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189044</t>
+          <t xml:space="preserve">311190150</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-08</t>
+          <t xml:space="preserve">2026-07-14</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,40 +10466,40 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 2</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339443</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J140">
-        <v>206</v>
+        <v>1337</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190150</t>
+          <t xml:space="preserve">311190370</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-14</t>
+          <t xml:space="preserve">2026-07-15</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 4</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339443</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,21 +10560,21 @@
         </is>
       </c>
       <c r="J141">
-        <v>5980</v>
+        <v>400</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190150</t>
+          <t xml:space="preserve">311190370</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-14</t>
+          <t xml:space="preserve">2026-07-15</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10631,11 +10631,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J142">
-        <v>1337</v>
+        <v>954</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10706,11 +10706,11 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J143">
-        <v>400</v>
+        <v>957</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10766,40 +10766,40 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Korsbakken 9</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">3339512</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>954</v>
+        <v>442</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190370</t>
+          <t xml:space="preserve">311200372</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-15</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,50 +10841,50 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Savværksvej 5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">403587, 403588</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>957</v>
+        <v>750</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190370</t>
+          <t xml:space="preserve">311202307</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-15</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10916,40 +10916,40 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsbakken 9</t>
+          <t xml:space="preserve">H I Biesgade 4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339512</t>
+          <t xml:space="preserve">5601067</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J146">
-        <v>442</v>
+        <v>287</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200372</t>
+          <t xml:space="preserve">311203630</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Savværksvej 5</t>
+          <t xml:space="preserve">Rugmarken 2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">403587, 403588</t>
+          <t xml:space="preserve">3351204</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>750</v>
+        <v>497</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202307</t>
+          <t xml:space="preserve">311206994</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">H I Biesgade 4</t>
+          <t xml:space="preserve">Skolekrogen 2A</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,30 +11076,30 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601067</t>
+          <t xml:space="preserve">3351970</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>287</v>
+        <v>3982</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203630</t>
+          <t xml:space="preserve">311206964</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 2</t>
+          <t xml:space="preserve">Nyvangsvej 8</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351204</t>
+          <t xml:space="preserve">3356564</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>497</v>
+        <v>403</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206994</t>
+          <t xml:space="preserve">311207916</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolekrogen 2A</t>
+          <t xml:space="preserve">Søtofte 2A</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351970</t>
+          <t xml:space="preserve">4080676</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>3982</v>
+        <v>195</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206964</t>
+          <t xml:space="preserve">311207894</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,17 +11291,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangsvej 8</t>
+          <t xml:space="preserve">Daniavej 40</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356564</t>
+          <t xml:space="preserve">4078307</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>403</v>
+        <v>277</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207916</t>
+          <t xml:space="preserve">311212626</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,17 +11366,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søtofte 2A</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4080676</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,11 +11385,11 @@
         </is>
       </c>
       <c r="J152">
-        <v>195</v>
+        <v>543</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207894</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,30 +11441,30 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniavej 40</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078307</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>277</v>
+        <v>418</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212626</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11531,11 +11531,11 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J154">
-        <v>543</v>
+        <v>663</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Bluhmesgade 19</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">3350443</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>418</v>
+        <v>1768</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311246240</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,30 +11666,30 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Digtervænget 46</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">5607088</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J156">
-        <v>663</v>
+        <v>538</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311248868</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,17 +11741,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bluhmesgade 19</t>
+          <t xml:space="preserve">Gl Hobrovej 3A</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3350443</t>
+          <t xml:space="preserve">8038852</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>1768</v>
+        <v>520</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246240</t>
+          <t xml:space="preserve">311248873</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digtervænget 46</t>
+          <t xml:space="preserve">Korsgade 2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607088</t>
+          <t xml:space="preserve">5600985</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>538</v>
+        <v>2360</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248868</t>
+          <t xml:space="preserve">311248882</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,17 +11891,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hobrovej 3A</t>
+          <t xml:space="preserve">Nordre Kajgade 1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038852</t>
+          <t xml:space="preserve">5600836</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,11 +11910,11 @@
         </is>
       </c>
       <c r="J159">
-        <v>520</v>
+        <v>850</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248873</t>
+          <t xml:space="preserve">311248866</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,17 +11966,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgade 2</t>
+          <t xml:space="preserve">Rosendals Alle 8</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600985</t>
+          <t xml:space="preserve">3356457</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>2360</v>
+        <v>733</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248882</t>
+          <t xml:space="preserve">311256463</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,30 +12041,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 1</t>
+          <t xml:space="preserve">Rosendals Alle 8</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600836</t>
+          <t xml:space="preserve">3356457</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J161">
-        <v>850</v>
+        <v>237</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248866</t>
+          <t xml:space="preserve">311256464</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,30 +12116,30 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosendals Alle 8</t>
+          <t xml:space="preserve">Skolegade 12</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356457</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J162">
-        <v>733</v>
+        <v>666</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256463</t>
+          <t xml:space="preserve">311258677</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,40 +12191,40 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosendals Alle 8</t>
+          <t xml:space="preserve">Rørholmsgade 8</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356457</t>
+          <t xml:space="preserve">5601048</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J163">
-        <v>237</v>
+        <v>488</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256464</t>
+          <t xml:space="preserve">311259494</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12</t>
+          <t xml:space="preserve">Fjordgade 12</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">5601049</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
-        <v>666</v>
+        <v>512</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258677</t>
+          <t xml:space="preserve">311261189</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørholmsgade 8</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601048</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,21 +12360,21 @@
         </is>
       </c>
       <c r="J165">
-        <v>488</v>
+        <v>1986</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259494</t>
+          <t xml:space="preserve">311261205</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,30 +12416,30 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 12</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601049</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J166">
-        <v>512</v>
+        <v>444</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261189</t>
+          <t xml:space="preserve">311261207</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,17 +12491,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Sjællandsvej 15</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5601328</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>1986</v>
+        <v>1380</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261205</t>
+          <t xml:space="preserve">311261221</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,30 +12566,30 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>444</v>
+        <v>556</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261207</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsvej 15</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601328</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J169">
-        <v>1380</v>
+        <v>906</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261221</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,17 +12716,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Teglgade 6</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5605653</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,11 +12735,11 @@
         </is>
       </c>
       <c r="J170">
-        <v>556</v>
+        <v>621</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311261137</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>906</v>
+        <v>1994</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,30 +12866,30 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgade 6</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605653</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>621</v>
+        <v>757</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261137</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12956,11 +12956,11 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J173">
-        <v>1994</v>
+        <v>1368</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13031,11 +13031,11 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J174">
-        <v>757</v>
+        <v>2016</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13106,11 +13106,11 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J175">
-        <v>1368</v>
+        <v>540</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13181,11 +13181,11 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J176">
-        <v>2016</v>
+        <v>1876</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>540</v>
+        <v>834</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J178">
-        <v>1876</v>
+        <v>1326</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,30 +13391,30 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 19</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J179">
-        <v>834</v>
+        <v>1670</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286484</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,30 +13466,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 21</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J180">
-        <v>1326</v>
+        <v>2252</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286483</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 19</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,20 +13551,20 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>1670</v>
+        <v>401</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286484</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,20 +13626,20 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J182">
-        <v>2252</v>
+        <v>401</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286483</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J183">
@@ -13781,11 +13781,11 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J184">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13856,11 +13856,11 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J185">
-        <v>401</v>
+        <v>640</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13931,11 +13931,11 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J186">
-        <v>448</v>
+        <v>354</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -14006,15 +14006,15 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J187">
-        <v>640</v>
+        <v>296</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311286481</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14066,30 +14066,30 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Stadionvej 5</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">8379978</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J188">
-        <v>354</v>
+        <v>11962</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311288954</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Fayesgade 14A</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,20 +14151,20 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J189">
-        <v>296</v>
+        <v>1500</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286481</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,30 +14216,30 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 5</t>
+          <t xml:space="preserve">Fayesgade 14B</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">8379978</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J190">
-        <v>11962</v>
+        <v>2442</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288954</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14A</t>
+          <t xml:space="preserve">Fayesgade 14D</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14306,11 +14306,11 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J191">
-        <v>1500</v>
+        <v>740</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14366,30 +14366,30 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14B</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J192">
-        <v>2442</v>
+        <v>1229</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,30 +14441,30 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14D</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J193">
-        <v>740</v>
+        <v>1980</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14531,11 +14531,11 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J194">
-        <v>1229</v>
+        <v>1065</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14606,11 +14606,11 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J195">
-        <v>1980</v>
+        <v>535</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -14681,11 +14681,11 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J196">
-        <v>1065</v>
+        <v>535</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14756,11 +14756,11 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J197">
-        <v>535</v>
+        <v>377</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14816,30 +14816,30 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Ålborgvej 17A</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3357310</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J198">
-        <v>535</v>
+        <v>309</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311301379</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-07</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,30 +14891,30 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Tempovej 1</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3356517</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J199">
-        <v>377</v>
+        <v>3384</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311303211</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-16</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 17A</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357310</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>309</v>
+        <v>777</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301379</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-07</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,30 +15041,30 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempovej 1</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356517</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J201">
-        <v>3384</v>
+        <v>689</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311303211</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-16</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,17 +15116,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Sverigesvej 3</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">8516334</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,11 +15135,11 @@
         </is>
       </c>
       <c r="J202">
-        <v>777</v>
+        <v>2329</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311307590</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Vinkelvej 3</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">3356821</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J203">
-        <v>689</v>
+        <v>69</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311311580</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-05-02</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverigesvej 3</t>
+          <t xml:space="preserve">Timandsvej 25A</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8516334</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -15285,11 +15285,11 @@
         </is>
       </c>
       <c r="J204">
-        <v>2329</v>
+        <v>3913</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307590</t>
+          <t xml:space="preserve">311317939</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 3</t>
+          <t xml:space="preserve">Timandsvej 25D</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,20 +15351,20 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356821</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J205">
-        <v>69</v>
+        <v>546</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311311580</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-02</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25A</t>
+          <t xml:space="preserve">Timandsvej 25E</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15431,15 +15431,15 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J206">
-        <v>3913</v>
+        <v>546</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317939</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15491,30 +15491,30 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25D</t>
+          <t xml:space="preserve">Thoruphedevej 3</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7567144</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J207">
-        <v>546</v>
+        <v>297</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311319914</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,30 +15566,30 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25E</t>
+          <t xml:space="preserve">Oxendalen 15B</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7996792</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J208">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311320212</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoruphedevej 3</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">7567144</t>
+          <t xml:space="preserve">403144</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,11 +15660,11 @@
         </is>
       </c>
       <c r="J209">
-        <v>297</v>
+        <v>2635</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319914</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-12</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,30 +15716,30 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15B</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">7996792</t>
+          <t xml:space="preserve">403144, 403145</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J210">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320212</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15801,16 +15801,16 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144</t>
+          <t xml:space="preserve">403145</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J211">
-        <v>2635</v>
+        <v>462</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Myhlenbergvej 16A</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,20 +15876,20 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144, 403145</t>
+          <t xml:space="preserve">751286</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J212">
-        <v>612</v>
+        <v>150</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321692</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-20</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,20 +15951,20 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">403145</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J213">
-        <v>462</v>
+        <v>5917</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16A</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,20 +16026,20 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">751286</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J214">
-        <v>150</v>
+        <v>1420</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321692</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-20</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Rugmarken 5</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">10050818</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>5917</v>
+        <v>960</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311323471</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,30 +16166,30 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Bernadottegården 60</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J216">
-        <v>1420</v>
+        <v>189</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,30 +16241,30 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 5</t>
+          <t xml:space="preserve">Bernadottegården 61</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050818</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J217">
-        <v>960</v>
+        <v>189</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323471</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-28</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 60</t>
+          <t xml:space="preserve">Bernadottegården 66</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J218">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 61</t>
+          <t xml:space="preserve">Bernadottegården 67</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16406,11 +16406,11 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J219">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 66</t>
+          <t xml:space="preserve">Bernadottegården 72</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16481,11 +16481,11 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J220">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 67</t>
+          <t xml:space="preserve">Bernadottegården 75</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J221">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 72</t>
+          <t xml:space="preserve">Bernadottegården 80</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J222">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 75</t>
+          <t xml:space="preserve">Bernadottegården 83</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J223">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 80</t>
+          <t xml:space="preserve">Bernadottegården 88</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16781,11 +16781,11 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J224">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 83</t>
+          <t xml:space="preserve">Bernadottegården 94</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16856,15 +16856,15 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J225">
-        <v>252</v>
+        <v>5059</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311324163</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16916,40 +16916,40 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 88</t>
+          <t xml:space="preserve">Edderupvej 3</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">4078847</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J226">
-        <v>189</v>
+        <v>802</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311329619</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 94</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -17010,11 +17010,11 @@
         </is>
       </c>
       <c r="J227">
-        <v>5059</v>
+        <v>709</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324163</t>
+          <t xml:space="preserve">311340955</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edderupvej 3</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -17076,30 +17076,30 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078847</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J228">
-        <v>802</v>
+        <v>450</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329619</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-09</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17156,15 +17156,15 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J229">
-        <v>709</v>
+        <v>450</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340955</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J230">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J231">
@@ -17366,40 +17366,40 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Skolebakken 4B</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">751527, 4089217</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J232">
-        <v>450</v>
+        <v>268</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311382849</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,40 +17441,40 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Tobberupvej 8</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">8925025</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J233">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311499497</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,40 +17516,40 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 4B</t>
+          <t xml:space="preserve">Solvej 10</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">751527, 4089217</t>
+          <t xml:space="preserve">1808922</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J234">
-        <v>268</v>
+        <v>1431</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382849</t>
+          <t xml:space="preserve">311574350</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">Hus Check ApS</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobberupvej 8</t>
+          <t xml:space="preserve">Skivevej 27</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17601,30 +17601,30 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925025</t>
+          <t xml:space="preserve">405931, 100798376</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J235">
-        <v>350</v>
+        <v>293</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311499497</t>
+          <t xml:space="preserve">311609330</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-01</t>
+          <t xml:space="preserve">2032-06-21</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,40 +17666,40 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvej 10</t>
+          <t xml:space="preserve">Østergade 21</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808922</t>
+          <t xml:space="preserve">403157, 403158</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J236">
-        <v>1431</v>
+        <v>501</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574350</t>
+          <t xml:space="preserve">311627846</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hus Check ApS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skivevej 27</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">405931, 100798376</t>
+          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>293</v>
+        <v>5995</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609330</t>
+          <t xml:space="preserve">311646437</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-21</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,17 +17816,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 21</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">403157, 403158</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -17835,21 +17835,21 @@
         </is>
       </c>
       <c r="J238">
-        <v>501</v>
+        <v>391</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311627846</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-14</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,40 +17891,40 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J239">
-        <v>5995</v>
+        <v>925</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646437</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17981,11 +17981,11 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J240">
-        <v>391</v>
+        <v>2948</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -18056,11 +18056,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J241">
-        <v>925</v>
+        <v>800</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -18131,11 +18131,11 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J242">
-        <v>2948</v>
+        <v>451</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -18206,11 +18206,11 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J243">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -18266,40 +18266,40 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Himmerlandsgade 9</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">8603975</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J244">
-        <v>451</v>
+        <v>3721</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311670894</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Håndværkerparken 2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,30 +18351,30 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">5602463</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
-        <v>825</v>
+        <v>586</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311688591</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,30 +18416,30 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandsgade 9</t>
+          <t xml:space="preserve">Søndre Ringvej 11</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">8603975</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J246">
-        <v>3721</v>
+        <v>341</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670894</t>
+          <t xml:space="preserve">311688585</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Håndværkerparken 2</t>
+          <t xml:space="preserve">Kirkegårdsvej 3A</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602463</t>
+          <t xml:space="preserve">3346084</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,21 +18510,21 @@
         </is>
       </c>
       <c r="J247">
-        <v>586</v>
+        <v>163</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688591</t>
+          <t xml:space="preserve">311733666</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-01-17</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 11</t>
+          <t xml:space="preserve">Adelgade 30B</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18576,30 +18576,30 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">5601052</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J248">
-        <v>341</v>
+        <v>638</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688585</t>
+          <t xml:space="preserve">311790164</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,17 +18641,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegårdsvej 3A</t>
+          <t xml:space="preserve">Plantagevej 1</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346084</t>
+          <t xml:space="preserve">8611069</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -18660,21 +18660,21 @@
         </is>
       </c>
       <c r="J249">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733666</t>
+          <t xml:space="preserve">311790167</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-17</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,30 +18716,30 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30B</t>
+          <t xml:space="preserve">Plantagevej 10</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601052</t>
+          <t xml:space="preserve">8611069</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J250">
-        <v>638</v>
+        <v>67</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790164</t>
+          <t xml:space="preserve">311790167</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 1</t>
+          <t xml:space="preserve">Plantagevej 15A</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J251">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 10</t>
+          <t xml:space="preserve">Plantagevej 15C</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J252">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 15A</t>
+          <t xml:space="preserve">Plantagevej 15E</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J253">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 15C</t>
+          <t xml:space="preserve">Plantagevej 2</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J254">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 15E</t>
+          <t xml:space="preserve">Plantagevej 6</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J255">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 2</t>
+          <t xml:space="preserve">Plantagevej 9</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19181,7 +19181,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J256">
@@ -19241,30 +19241,30 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 6</t>
+          <t xml:space="preserve">Søndre Kajgade 18A</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">8611069</t>
+          <t xml:space="preserve">5600779, 100891198</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J257">
-        <v>67</v>
+        <v>1062</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790167</t>
+          <t xml:space="preserve">311790163</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 9</t>
+          <t xml:space="preserve">Finlandsvej 14</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19326,20 +19326,20 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">8611069</t>
+          <t xml:space="preserve">10067706</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J258">
-        <v>67</v>
+        <v>214</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790167</t>
+          <t xml:space="preserve">311829972</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2035-05-07</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Kajgade 18A</t>
+          <t xml:space="preserve">Nordre Kajgade 3A</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600779, 100891198</t>
+          <t xml:space="preserve">7006509</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -19410,11 +19410,11 @@
         </is>
       </c>
       <c r="J259">
-        <v>1062</v>
+        <v>225</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790163</t>
+          <t xml:space="preserve">311829971</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2035-05-07</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,30 +19466,30 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finlandsvej 14</t>
+          <t xml:space="preserve">Houvej 4</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067706</t>
+          <t xml:space="preserve">7010134</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829972</t>
+          <t xml:space="preserve">311871711</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-07</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,30 +19541,30 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 3A</t>
+          <t xml:space="preserve">Hvarrevej 19</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006509</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J261">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829971</t>
+          <t xml:space="preserve">311871713</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-07</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,30 +19616,30 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houvej 4</t>
+          <t xml:space="preserve">Fjordgade 7</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010134</t>
+          <t xml:space="preserve">7440925, 100764817</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J262">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871711</t>
+          <t xml:space="preserve">311879402</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,30 +19691,30 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 19</t>
+          <t xml:space="preserve">Dorrelundsvej 3</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">4079414</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J263">
-        <v>315</v>
+        <v>60</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871713</t>
+          <t xml:space="preserve">311887002</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,40 +19766,40 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 7</t>
+          <t xml:space="preserve">Havnen 42</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">7440925, 100764817</t>
+          <t xml:space="preserve">751454, 8603833</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J264">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879402</t>
+          <t xml:space="preserve">311887010</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,35 +19841,35 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dorrelundsvej 3</t>
+          <t xml:space="preserve">Havnen 43</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">4079414</t>
+          <t xml:space="preserve">8603833</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J265">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887002</t>
+          <t xml:space="preserve">311887010</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 42</t>
+          <t xml:space="preserve">Havnen 44</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,16 +19926,16 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">751454, 8603833</t>
+          <t xml:space="preserve">751468, 8603833</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J266">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -19991,35 +19991,35 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 43</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">8603833</t>
+          <t xml:space="preserve">5605751</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J267">
-        <v>112</v>
+        <v>357</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887010</t>
+          <t xml:space="preserve">311887008</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 44</t>
+          <t xml:space="preserve">Stadionvej 9A</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,25 +20076,25 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">751468, 8603833</t>
+          <t xml:space="preserve">100024816</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J268">
-        <v>178</v>
+        <v>339</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887010</t>
+          <t xml:space="preserve">311887007</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Storegade 52</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20151,7 +20151,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605751</t>
+          <t xml:space="preserve">4078682</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -20160,11 +20160,11 @@
         </is>
       </c>
       <c r="J269">
-        <v>357</v>
+        <v>210</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887008</t>
+          <t xml:space="preserve">311887003</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9A</t>
+          <t xml:space="preserve">Gl Visborgvej 21</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">100024816</t>
+          <t xml:space="preserve">3356303</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -20235,11 +20235,11 @@
         </is>
       </c>
       <c r="J270">
-        <v>339</v>
+        <v>510</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887007</t>
+          <t xml:space="preserve">311891993</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-01</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,30 +20291,30 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 52</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078682</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J271">
-        <v>210</v>
+        <v>468</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887003</t>
+          <t xml:space="preserve">311896233</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,30 +20366,30 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Visborgvej 21</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356303</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J272">
-        <v>510</v>
+        <v>235</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311891993</t>
+          <t xml:space="preserve">311896237</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-01</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Døstrupvej 33A</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20456,15 +20456,15 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J273">
-        <v>468</v>
+        <v>659</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896233</t>
+          <t xml:space="preserve">311896228</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Døstrupvej 21</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,20 +20526,20 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">100036624</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J274">
-        <v>235</v>
+        <v>1670</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896234</t>
+          <t xml:space="preserve">311898865</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33A</t>
+          <t xml:space="preserve">Kirketoften 5</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20601,20 +20601,20 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">5602982</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J275">
-        <v>659</v>
+        <v>2050</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896228</t>
+          <t xml:space="preserve">311898863</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,17 +20666,17 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 21</t>
+          <t xml:space="preserve">Vestergade 4</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">100036624</t>
+          <t xml:space="preserve">3355780</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -20685,11 +20685,11 @@
         </is>
       </c>
       <c r="J276">
-        <v>1670</v>
+        <v>2199</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898865</t>
+          <t xml:space="preserve">311899310</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-06</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 5</t>
+          <t xml:space="preserve">Christiansgade 10</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602982</t>
+          <t xml:space="preserve">5600572</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -20760,11 +20760,11 @@
         </is>
       </c>
       <c r="J277">
-        <v>2050</v>
+        <v>881</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898863</t>
+          <t xml:space="preserve">311903717</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20816,30 +20816,30 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 4</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355780</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J278">
-        <v>2199</v>
+        <v>786</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899310</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-06</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansgade 10</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -20901,20 +20901,20 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600572</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J279">
-        <v>881</v>
+        <v>369</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903717</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20981,11 +20981,11 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J280">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -21056,11 +21056,11 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J281">
-        <v>369</v>
+        <v>2989</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -21131,11 +21131,11 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J282">
-        <v>770</v>
+        <v>139</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -21206,11 +21206,11 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J283">
-        <v>2989</v>
+        <v>1421</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -21281,11 +21281,11 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J284">
-        <v>139</v>
+        <v>479</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Gettrupvej 3</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -21351,20 +21351,20 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7007800</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J285">
-        <v>1421</v>
+        <v>1127</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918912</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Ulstrupvej 3C</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21426,20 +21426,20 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7934937</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J286">
-        <v>479</v>
+        <v>635</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918911</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gettrupvej 3</t>
+          <t xml:space="preserve">Adelgade 28A</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -21501,20 +21501,20 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007800</t>
+          <t xml:space="preserve">5600946</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J287">
-        <v>1127</v>
+        <v>1095</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918912</t>
+          <t xml:space="preserve">311925680</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulstrupvej 3C</t>
+          <t xml:space="preserve">Adelgade 30A</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">7934937</t>
+          <t xml:space="preserve">5601054</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -21585,11 +21585,11 @@
         </is>
       </c>
       <c r="J288">
-        <v>635</v>
+        <v>400</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918911</t>
+          <t xml:space="preserve">311925679</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">

--- a/public/exports-from-60/29189455.xlsx
+++ b/public/exports-from-60/29189455.xlsx
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kønigsfeldtsvej 7</t>
+          <t xml:space="preserve">Kirkevej 13</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4077985</t>
+          <t xml:space="preserve">7864866</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
-        <v>2226</v>
+        <v>360</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179221</t>
+          <t xml:space="preserve">311181429</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27</t>
+          <t xml:space="preserve">2026-06-07</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 13</t>
+          <t xml:space="preserve">Kirkevej 23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J127">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 23</t>
+          <t xml:space="preserve">Kirkevej 9</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9581,15 +9581,15 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J128">
-        <v>360</v>
+        <v>2671</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181429</t>
+          <t xml:space="preserve">311181419</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9641,17 +9641,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 9</t>
+          <t xml:space="preserve">Kærvej 30</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">7864866</t>
+          <t xml:space="preserve">8043516</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>2671</v>
+        <v>223</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181419</t>
+          <t xml:space="preserve">311184922</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-07</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9731,15 +9731,15 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J130">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184922</t>
+          <t xml:space="preserve">311184913</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9806,15 +9806,15 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J131">
-        <v>220</v>
+        <v>1366</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184913</t>
+          <t xml:space="preserve">311184922</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 30</t>
+          <t xml:space="preserve">Døstrupvej 1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8043516</t>
+          <t xml:space="preserve">3346368</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J132">
-        <v>1366</v>
+        <v>506</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184922</t>
+          <t xml:space="preserve">311189004</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9956,15 +9956,15 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J133">
-        <v>506</v>
+        <v>824</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189004</t>
+          <t xml:space="preserve">311189007</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 1</t>
+          <t xml:space="preserve">Døstrupvej 3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10031,15 +10031,15 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J134">
-        <v>824</v>
+        <v>228</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189007</t>
+          <t xml:space="preserve">311189034</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3</t>
+          <t xml:space="preserve">Døstrupvej 3A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,20 +10101,20 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346368</t>
+          <t xml:space="preserve">751530, 3346372</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J135">
-        <v>228</v>
+        <v>1064</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189034</t>
+          <t xml:space="preserve">311189044</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10181,11 +10181,11 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J136">
-        <v>1064</v>
+        <v>667</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10241,30 +10241,30 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3A</t>
+          <t xml:space="preserve">Vikingvej 2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">751530, 3346372</t>
+          <t xml:space="preserve">3339443</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J137">
-        <v>667</v>
+        <v>206</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189044</t>
+          <t xml:space="preserve">311190150</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-08</t>
+          <t xml:space="preserve">2026-07-14</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 2</t>
+          <t xml:space="preserve">Vikingvej 4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10331,11 +10331,11 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J138">
-        <v>206</v>
+        <v>5980</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10391,40 +10391,40 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 4</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339443</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J139">
-        <v>5980</v>
+        <v>1337</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190150</t>
+          <t xml:space="preserve">311190370</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-14</t>
+          <t xml:space="preserve">2026-07-15</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J140">
-        <v>1337</v>
+        <v>400</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J141">
-        <v>400</v>
+        <v>954</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10631,11 +10631,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J142">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10691,40 +10691,40 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Korsbakken 9</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">3339512</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>957</v>
+        <v>442</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190370</t>
+          <t xml:space="preserve">311200372</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-15</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsbakken 9</t>
+          <t xml:space="preserve">Savværksvej 5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339512</t>
+          <t xml:space="preserve">403587, 403588</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>442</v>
+        <v>750</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200372</t>
+          <t xml:space="preserve">311202307</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Savværksvej 5</t>
+          <t xml:space="preserve">H I Biesgade 4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,40 +10851,40 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">403587, 403588</t>
+          <t xml:space="preserve">5601067</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J145">
-        <v>750</v>
+        <v>287</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202307</t>
+          <t xml:space="preserve">311203630</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10916,40 +10916,40 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">H I Biesgade 4</t>
+          <t xml:space="preserve">Rugmarken 2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601067</t>
+          <t xml:space="preserve">3351204</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>287</v>
+        <v>497</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203630</t>
+          <t xml:space="preserve">311206994</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 2</t>
+          <t xml:space="preserve">Skolekrogen 2A</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351204</t>
+          <t xml:space="preserve">3351970</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>497</v>
+        <v>3982</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206994</t>
+          <t xml:space="preserve">311206964</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolekrogen 2A</t>
+          <t xml:space="preserve">Nyvangsvej 8</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351970</t>
+          <t xml:space="preserve">3356564</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>3982</v>
+        <v>403</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206964</t>
+          <t xml:space="preserve">311207916</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangsvej 8</t>
+          <t xml:space="preserve">Søtofte 2A</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356564</t>
+          <t xml:space="preserve">4080676</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>403</v>
+        <v>195</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207916</t>
+          <t xml:space="preserve">311207894</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,17 +11216,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søtofte 2A</t>
+          <t xml:space="preserve">Daniavej 40</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4080676</t>
+          <t xml:space="preserve">4078307</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>195</v>
+        <v>277</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207894</t>
+          <t xml:space="preserve">311212626</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,17 +11291,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniavej 40</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078307</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>277</v>
+        <v>543</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212626</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11381,11 +11381,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J152">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11456,11 +11456,11 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J153">
-        <v>418</v>
+        <v>663</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Bluhmesgade 19</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,20 +11526,20 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">3350443</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>663</v>
+        <v>1768</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311246240</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bluhmesgade 19</t>
+          <t xml:space="preserve">Digtervænget 46</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3350443</t>
+          <t xml:space="preserve">5607088</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>1768</v>
+        <v>538</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246240</t>
+          <t xml:space="preserve">311248868</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digtervænget 46</t>
+          <t xml:space="preserve">Gl Hobrovej 3A</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607088</t>
+          <t xml:space="preserve">8038852</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248868</t>
+          <t xml:space="preserve">311248873</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,17 +11741,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hobrovej 3A</t>
+          <t xml:space="preserve">Korsgade 2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038852</t>
+          <t xml:space="preserve">5600985</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>520</v>
+        <v>2360</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248873</t>
+          <t xml:space="preserve">311248882</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgade 2</t>
+          <t xml:space="preserve">Nordre Kajgade 1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600985</t>
+          <t xml:space="preserve">5600836</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>2360</v>
+        <v>850</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248882</t>
+          <t xml:space="preserve">311248866</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,17 +11891,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 1</t>
+          <t xml:space="preserve">Rosendals Alle 8</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600836</t>
+          <t xml:space="preserve">3356457</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,11 +11910,11 @@
         </is>
       </c>
       <c r="J159">
-        <v>850</v>
+        <v>733</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248866</t>
+          <t xml:space="preserve">311256463</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11981,15 +11981,15 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J160">
-        <v>733</v>
+        <v>237</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256463</t>
+          <t xml:space="preserve">311256464</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,30 +12041,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosendals Alle 8</t>
+          <t xml:space="preserve">Skolegade 12</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356457</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J161">
-        <v>237</v>
+        <v>666</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256464</t>
+          <t xml:space="preserve">311258677</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12</t>
+          <t xml:space="preserve">Rørholmsgade 8</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,30 +12126,30 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">5601048</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>666</v>
+        <v>488</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258677</t>
+          <t xml:space="preserve">311259494</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørholmsgade 8</t>
+          <t xml:space="preserve">Fjordgade 12</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601048</t>
+          <t xml:space="preserve">5601049</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,21 +12210,21 @@
         </is>
       </c>
       <c r="J163">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259494</t>
+          <t xml:space="preserve">311261189</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 12</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601049</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>512</v>
+        <v>1986</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261189</t>
+          <t xml:space="preserve">311261205</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12356,15 +12356,15 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J165">
-        <v>1986</v>
+        <v>444</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261205</t>
+          <t xml:space="preserve">311261207</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,30 +12416,30 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Sjællandsvej 15</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5601328</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>444</v>
+        <v>1380</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261207</t>
+          <t xml:space="preserve">311261221</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsvej 15</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601328</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>1380</v>
+        <v>556</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261221</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12581,11 +12581,11 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J168">
-        <v>556</v>
+        <v>906</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12641,30 +12641,30 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Teglgade 6</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5605653</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>906</v>
+        <v>621</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311261137</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,17 +12716,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgade 6</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605653</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,11 +12735,11 @@
         </is>
       </c>
       <c r="J170">
-        <v>621</v>
+        <v>1994</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261137</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12806,11 +12806,11 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J171">
-        <v>1994</v>
+        <v>757</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12881,11 +12881,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J172">
-        <v>757</v>
+        <v>1368</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12956,11 +12956,11 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J173">
-        <v>1368</v>
+        <v>2016</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13031,11 +13031,11 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J174">
-        <v>2016</v>
+        <v>540</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13106,11 +13106,11 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J175">
-        <v>540</v>
+        <v>1876</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J176">
-        <v>1876</v>
+        <v>834</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13256,11 +13256,11 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J177">
-        <v>834</v>
+        <v>1326</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 19</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J178">
-        <v>1326</v>
+        <v>1670</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286484</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 19</t>
+          <t xml:space="preserve">Amerikavej 21</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13406,15 +13406,15 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J179">
-        <v>1670</v>
+        <v>2252</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286484</t>
+          <t xml:space="preserve">311286483</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,20 +13476,20 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J180">
-        <v>2252</v>
+        <v>401</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286483</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J181">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J182">
@@ -13706,11 +13706,11 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J183">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13781,11 +13781,11 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J184">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13856,11 +13856,11 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J185">
-        <v>640</v>
+        <v>354</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13931,15 +13931,15 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J186">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311286481</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13991,30 +13991,30 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Stadionvej 5</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">8379978</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>296</v>
+        <v>11962</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286481</t>
+          <t xml:space="preserve">311288954</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,17 +14066,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 5</t>
+          <t xml:space="preserve">Fayesgade 14A</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">8379978</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,11 +14085,11 @@
         </is>
       </c>
       <c r="J188">
-        <v>11962</v>
+        <v>1500</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288954</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14A</t>
+          <t xml:space="preserve">Fayesgade 14B</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14156,11 +14156,11 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J189">
-        <v>1500</v>
+        <v>2442</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14B</t>
+          <t xml:space="preserve">Fayesgade 14D</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14231,11 +14231,11 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J190">
-        <v>2442</v>
+        <v>740</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14291,30 +14291,30 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14D</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J191">
-        <v>740</v>
+        <v>1229</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14381,11 +14381,11 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J192">
-        <v>1229</v>
+        <v>1980</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -14456,11 +14456,11 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J193">
-        <v>1980</v>
+        <v>1065</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14531,11 +14531,11 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J194">
-        <v>1065</v>
+        <v>535</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J195">
@@ -14681,11 +14681,11 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J196">
-        <v>535</v>
+        <v>377</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14741,30 +14741,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Ålborgvej 17A</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3357310</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>377</v>
+        <v>309</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311301379</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-07</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 17A</t>
+          <t xml:space="preserve">Tempovej 1</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357310</t>
+          <t xml:space="preserve">3356517</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>309</v>
+        <v>3384</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301379</t>
+          <t xml:space="preserve">311303211</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-07</t>
+          <t xml:space="preserve">2028-03-16</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempovej 1</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356517</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,11 +14910,11 @@
         </is>
       </c>
       <c r="J199">
-        <v>3384</v>
+        <v>777</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311303211</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-16</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14981,11 +14981,11 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J200">
-        <v>777</v>
+        <v>689</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -15041,30 +15041,30 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Sverigesvej 3</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">8516334</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J201">
-        <v>689</v>
+        <v>2329</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311307590</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverigesvej 3</t>
+          <t xml:space="preserve">Vinkelvej 3</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">8516334</t>
+          <t xml:space="preserve">3356821</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,11 +15135,11 @@
         </is>
       </c>
       <c r="J202">
-        <v>2329</v>
+        <v>69</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307590</t>
+          <t xml:space="preserve">311311580</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-05-02</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 3</t>
+          <t xml:space="preserve">Timandsvej 25A</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356821</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -15210,11 +15210,11 @@
         </is>
       </c>
       <c r="J203">
-        <v>69</v>
+        <v>3913</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311311580</t>
+          <t xml:space="preserve">311317939</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-02</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25A</t>
+          <t xml:space="preserve">Timandsvej 25D</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15281,15 +15281,15 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J204">
-        <v>3913</v>
+        <v>546</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317939</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25D</t>
+          <t xml:space="preserve">Timandsvej 25E</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J205">
@@ -15416,30 +15416,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25E</t>
+          <t xml:space="preserve">Thoruphedevej 3</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7567144</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>546</v>
+        <v>297</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311319914</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,17 +15491,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoruphedevej 3</t>
+          <t xml:space="preserve">Oxendalen 15B</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">7567144</t>
+          <t xml:space="preserve">7996792</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>297</v>
+        <v>582</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319914</t>
+          <t xml:space="preserve">311320212</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-12</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,17 +15566,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15B</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">7996792</t>
+          <t xml:space="preserve">403144</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,11 +15585,11 @@
         </is>
       </c>
       <c r="J208">
-        <v>582</v>
+        <v>2635</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320212</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15651,16 +15651,16 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144</t>
+          <t xml:space="preserve">403144, 403145</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J209">
-        <v>2635</v>
+        <v>612</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144, 403145</t>
+          <t xml:space="preserve">403145</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J210">
-        <v>612</v>
+        <v>462</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Myhlenbergvej 16A</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,20 +15801,20 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">403145</t>
+          <t xml:space="preserve">751286</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J211">
-        <v>462</v>
+        <v>150</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321692</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-20</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16A</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,20 +15876,20 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">751286</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J212">
-        <v>150</v>
+        <v>5917</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321692</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-20</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15956,11 +15956,11 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J213">
-        <v>5917</v>
+        <v>1420</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Rugmarken 5</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,20 +16026,20 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">10050818</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J214">
-        <v>1420</v>
+        <v>960</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311323471</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,30 +16091,30 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 5</t>
+          <t xml:space="preserve">Bernadottegården 60</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050818</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J215">
-        <v>960</v>
+        <v>189</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323471</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-28</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 60</t>
+          <t xml:space="preserve">Bernadottegården 61</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J216">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 61</t>
+          <t xml:space="preserve">Bernadottegården 66</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16256,7 +16256,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J217">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 66</t>
+          <t xml:space="preserve">Bernadottegården 67</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16331,11 +16331,11 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J218">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 67</t>
+          <t xml:space="preserve">Bernadottegården 72</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J219">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 72</t>
+          <t xml:space="preserve">Bernadottegården 75</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J220">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 75</t>
+          <t xml:space="preserve">Bernadottegården 80</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J221">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 80</t>
+          <t xml:space="preserve">Bernadottegården 83</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J222">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 83</t>
+          <t xml:space="preserve">Bernadottegården 88</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16706,11 +16706,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J223">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 88</t>
+          <t xml:space="preserve">Bernadottegården 94</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16781,15 +16781,15 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J224">
-        <v>189</v>
+        <v>5059</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311324163</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16841,40 +16841,40 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 94</t>
+          <t xml:space="preserve">Edderupvej 3</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">4078847</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J225">
-        <v>5059</v>
+        <v>802</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324163</t>
+          <t xml:space="preserve">311329619</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edderupvej 3</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,30 +16926,30 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078847</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J226">
-        <v>802</v>
+        <v>709</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329619</t>
+          <t xml:space="preserve">311340955</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-09</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -17006,15 +17006,15 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J227">
-        <v>709</v>
+        <v>450</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340955</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J228">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J229">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J230">
@@ -17291,40 +17291,40 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Skolebakken 4B</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">751527, 4089217</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J231">
-        <v>450</v>
+        <v>268</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311382849</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,40 +17366,40 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 4B</t>
+          <t xml:space="preserve">Tobberupvej 8</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">751527, 4089217</t>
+          <t xml:space="preserve">8925025</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J232">
-        <v>268</v>
+        <v>350</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382849</t>
+          <t xml:space="preserve">311499497</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobberupvej 8</t>
+          <t xml:space="preserve">Solvej 10</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17451,30 +17451,30 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925025</t>
+          <t xml:space="preserve">1808922</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J233">
-        <v>350</v>
+        <v>1431</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311499497</t>
+          <t xml:space="preserve">311574350</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Hus Check ApS</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-01</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvej 10</t>
+          <t xml:space="preserve">Skivevej 27</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,30 +17526,30 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808922</t>
+          <t xml:space="preserve">405931, 100798376</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J234">
-        <v>1431</v>
+        <v>293</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574350</t>
+          <t xml:space="preserve">311609330</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hus Check ApS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-06-21</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,30 +17591,30 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skivevej 27</t>
+          <t xml:space="preserve">Østergade 21</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">405931, 100798376</t>
+          <t xml:space="preserve">403157, 403158</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J235">
-        <v>293</v>
+        <v>501</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609330</t>
+          <t xml:space="preserve">311627846</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-21</t>
+          <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,17 +17666,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 21</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">403157, 403158</t>
+          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -17685,11 +17685,11 @@
         </is>
       </c>
       <c r="J236">
-        <v>501</v>
+        <v>5995</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311627846</t>
+          <t xml:space="preserve">311646437</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-14</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,17 +17741,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -17760,21 +17760,21 @@
         </is>
       </c>
       <c r="J237">
-        <v>5995</v>
+        <v>391</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646437</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17831,11 +17831,11 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J238">
-        <v>391</v>
+        <v>925</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -17906,11 +17906,11 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J239">
-        <v>925</v>
+        <v>2948</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -17981,11 +17981,11 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J240">
-        <v>2948</v>
+        <v>800</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -18056,11 +18056,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J241">
-        <v>800</v>
+        <v>451</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -18131,11 +18131,11 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J242">
-        <v>451</v>
+        <v>825</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -18191,40 +18191,40 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Himmerlandsgade 9</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">8603975</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J243">
-        <v>825</v>
+        <v>3721</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311670894</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,17 +18266,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandsgade 9</t>
+          <t xml:space="preserve">Håndværkerparken 2</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">8603975</t>
+          <t xml:space="preserve">5602463</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -18285,11 +18285,11 @@
         </is>
       </c>
       <c r="J244">
-        <v>3721</v>
+        <v>586</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670894</t>
+          <t xml:space="preserve">311688591</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Håndværkerparken 2</t>
+          <t xml:space="preserve">Søndre Ringvej 11</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,20 +18351,20 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602463</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J245">
-        <v>586</v>
+        <v>341</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688591</t>
+          <t xml:space="preserve">311688585</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 11</t>
+          <t xml:space="preserve">Kirkegårdsvej 3A</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18426,30 +18426,30 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">3346084</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J246">
-        <v>341</v>
+        <v>163</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688585</t>
+          <t xml:space="preserve">311733666</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-01-17</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegårdsvej 3A</t>
+          <t xml:space="preserve">Adelgade 30B</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346084</t>
+          <t xml:space="preserve">5601052</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,21 +18510,21 @@
         </is>
       </c>
       <c r="J247">
-        <v>163</v>
+        <v>638</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733666</t>
+          <t xml:space="preserve">311790164</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-17</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,17 +18566,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30B</t>
+          <t xml:space="preserve">Plantagevej 1</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601052</t>
+          <t xml:space="preserve">8611069</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -18585,11 +18585,11 @@
         </is>
       </c>
       <c r="J248">
-        <v>638</v>
+        <v>67</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790164</t>
+          <t xml:space="preserve">311790167</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 1</t>
+          <t xml:space="preserve">Plantagevej 10</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18656,7 +18656,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J249">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 10</t>
+          <t xml:space="preserve">Plantagevej 15A</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J250">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 15A</t>
+          <t xml:space="preserve">Plantagevej 15C</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J251">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 15C</t>
+          <t xml:space="preserve">Plantagevej 15E</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J252">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 15E</t>
+          <t xml:space="preserve">Plantagevej 2</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J253">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 2</t>
+          <t xml:space="preserve">Plantagevej 6</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J254">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 6</t>
+          <t xml:space="preserve">Plantagevej 9</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J255">
@@ -19166,30 +19166,30 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 9</t>
+          <t xml:space="preserve">Søndre Kajgade 18A</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">8611069</t>
+          <t xml:space="preserve">5600779, 100891198</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J256">
-        <v>67</v>
+        <v>1062</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790167</t>
+          <t xml:space="preserve">311790163</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19241,30 +19241,30 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Kajgade 18A</t>
+          <t xml:space="preserve">Finlandsvej 14</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600779, 100891198</t>
+          <t xml:space="preserve">10067706</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J257">
-        <v>1062</v>
+        <v>214</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790163</t>
+          <t xml:space="preserve">311829972</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2035-05-07</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,30 +19316,30 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finlandsvej 14</t>
+          <t xml:space="preserve">Nordre Kajgade 3A</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067706</t>
+          <t xml:space="preserve">7006509</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J258">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829972</t>
+          <t xml:space="preserve">311829971</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 3A</t>
+          <t xml:space="preserve">Houvej 4</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006509</t>
+          <t xml:space="preserve">7010134</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -19410,11 +19410,11 @@
         </is>
       </c>
       <c r="J259">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829971</t>
+          <t xml:space="preserve">311871711</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-07</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,30 +19466,30 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houvej 4</t>
+          <t xml:space="preserve">Hvarrevej 19</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010134</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J260">
-        <v>167</v>
+        <v>315</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871711</t>
+          <t xml:space="preserve">311871713</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19541,30 +19541,30 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 19</t>
+          <t xml:space="preserve">Fjordgade 7</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">7440925, 100764817</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J261">
-        <v>315</v>
+        <v>104</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871713</t>
+          <t xml:space="preserve">311879402</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,30 +19616,30 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 7</t>
+          <t xml:space="preserve">Dorrelundsvej 3</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">7440925, 100764817</t>
+          <t xml:space="preserve">4079414</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J262">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879402</t>
+          <t xml:space="preserve">311887002</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,35 +19691,35 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dorrelundsvej 3</t>
+          <t xml:space="preserve">Havnen 42</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">4079414</t>
+          <t xml:space="preserve">751454, 8603833</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J263">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887002</t>
+          <t xml:space="preserve">311887010</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 42</t>
+          <t xml:space="preserve">Havnen 43</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,16 +19776,16 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">751454, 8603833</t>
+          <t xml:space="preserve">8603833</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J264">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 43</t>
+          <t xml:space="preserve">Havnen 44</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,16 +19851,16 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">8603833</t>
+          <t xml:space="preserve">751468, 8603833</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J265">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -19916,35 +19916,35 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 44</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">751468, 8603833</t>
+          <t xml:space="preserve">5605751</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J266">
-        <v>178</v>
+        <v>357</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887010</t>
+          <t xml:space="preserve">311887008</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -19991,17 +19991,17 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Stadionvej 9A</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605751</t>
+          <t xml:space="preserve">100024816</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -20010,11 +20010,11 @@
         </is>
       </c>
       <c r="J267">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887008</t>
+          <t xml:space="preserve">311887007</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20066,17 +20066,17 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9A</t>
+          <t xml:space="preserve">Storegade 52</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">100024816</t>
+          <t xml:space="preserve">4078682</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -20085,11 +20085,11 @@
         </is>
       </c>
       <c r="J268">
-        <v>339</v>
+        <v>210</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887007</t>
+          <t xml:space="preserve">311887003</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20141,17 +20141,17 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 52</t>
+          <t xml:space="preserve">Gl Visborgvej 21</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078682</t>
+          <t xml:space="preserve">3356303</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -20160,11 +20160,11 @@
         </is>
       </c>
       <c r="J269">
-        <v>210</v>
+        <v>510</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887003</t>
+          <t xml:space="preserve">311891993</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-01</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,30 +20216,30 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Visborgvej 21</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356303</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J270">
-        <v>510</v>
+        <v>468</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311891993</t>
+          <t xml:space="preserve">311896233</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-01</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20306,15 +20306,15 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J271">
-        <v>468</v>
+        <v>235</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896233</t>
+          <t xml:space="preserve">311896234</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Døstrupvej 33A</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20381,15 +20381,15 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J272">
-        <v>235</v>
+        <v>659</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896237</t>
+          <t xml:space="preserve">311896228</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33A</t>
+          <t xml:space="preserve">Døstrupvej 21</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20451,20 +20451,20 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">100036624</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J273">
-        <v>659</v>
+        <v>1670</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896228</t>
+          <t xml:space="preserve">311898865</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 21</t>
+          <t xml:space="preserve">Kirketoften 5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">100036624</t>
+          <t xml:space="preserve">5602982</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -20535,11 +20535,11 @@
         </is>
       </c>
       <c r="J274">
-        <v>1670</v>
+        <v>2050</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898865</t>
+          <t xml:space="preserve">311898863</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20591,17 +20591,17 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 5</t>
+          <t xml:space="preserve">Vestergade 4</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602982</t>
+          <t xml:space="preserve">3355780</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -20610,11 +20610,11 @@
         </is>
       </c>
       <c r="J275">
-        <v>2050</v>
+        <v>2199</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898863</t>
+          <t xml:space="preserve">311899310</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-06</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,17 +20666,17 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 4</t>
+          <t xml:space="preserve">Christiansgade 10</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355780</t>
+          <t xml:space="preserve">5600572</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -20685,11 +20685,11 @@
         </is>
       </c>
       <c r="J276">
-        <v>2199</v>
+        <v>881</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899310</t>
+          <t xml:space="preserve">311903717</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-06</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansgade 10</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20751,20 +20751,20 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600572</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J277">
-        <v>881</v>
+        <v>786</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903717</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20831,11 +20831,11 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J278">
-        <v>786</v>
+        <v>369</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -20906,11 +20906,11 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J279">
-        <v>369</v>
+        <v>770</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -20981,11 +20981,11 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J280">
-        <v>770</v>
+        <v>2989</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -21056,11 +21056,11 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J281">
-        <v>2989</v>
+        <v>139</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -21131,11 +21131,11 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J282">
-        <v>139</v>
+        <v>1421</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -21206,11 +21206,11 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J283">
-        <v>1421</v>
+        <v>479</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Gettrupvej 3</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -21276,20 +21276,20 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7007800</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J284">
-        <v>479</v>
+        <v>1127</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918912</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gettrupvej 3</t>
+          <t xml:space="preserve">Ulstrupvej 3C</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -21351,20 +21351,20 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007800</t>
+          <t xml:space="preserve">7934937</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J285">
-        <v>1127</v>
+        <v>635</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918912</t>
+          <t xml:space="preserve">311918911</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulstrupvej 3C</t>
+          <t xml:space="preserve">Adelgade 28A</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21426,7 +21426,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">7934937</t>
+          <t xml:space="preserve">5600946</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -21435,11 +21435,11 @@
         </is>
       </c>
       <c r="J286">
-        <v>635</v>
+        <v>1095</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918911</t>
+          <t xml:space="preserve">311925680</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 28A</t>
+          <t xml:space="preserve">Adelgade 30A</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600946</t>
+          <t xml:space="preserve">5601054</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -21510,11 +21510,11 @@
         </is>
       </c>
       <c r="J287">
-        <v>1095</v>
+        <v>400</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925680</t>
+          <t xml:space="preserve">311925679</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21566,17 +21566,17 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30A</t>
+          <t xml:space="preserve">Kønigsfeldtsvej 7</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601054</t>
+          <t xml:space="preserve">4077985</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -21585,11 +21585,11 @@
         </is>
       </c>
       <c r="J288">
-        <v>400</v>
+        <v>2226</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925679</t>
+          <t xml:space="preserve">311926396</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-09-17</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">

--- a/public/exports-from-60/29189455.xlsx
+++ b/public/exports-from-60/29189455.xlsx
@@ -4316,26 +4316,26 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringvejen 1</t>
+          <t xml:space="preserve">Rugmarken 5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356242</t>
+          <t xml:space="preserve">10050818</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J58">
-        <v>460</v>
+        <v>252</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4406,11 +4406,11 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J59">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4466,26 +4466,26 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 5</t>
+          <t xml:space="preserve">Skibsgade 56A</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050818</t>
+          <t xml:space="preserve">751535, 5601057</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4541,26 +4541,26 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skibsgade 56A</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">751535, 5601057</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J61">
-        <v>181</v>
+        <v>388</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Skovvej 2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,16 +4626,16 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">7439691</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4691,17 +4691,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 2</t>
+          <t xml:space="preserve">Skydebanevej 1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7439691</t>
+          <t xml:space="preserve">751478, 3357417</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="J63">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skydebanevej 1</t>
+          <t xml:space="preserve">Solbjergvej 2B</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">751478, 3357417</t>
+          <t xml:space="preserve">100053286, 100920971</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="J64">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjergvej 2B</t>
+          <t xml:space="preserve">Stadionvej 25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,16 +4851,16 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">100053286, 100920971</t>
+          <t xml:space="preserve">751387, 3357680</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J65">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4931,11 +4931,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J66">
-        <v>230</v>
+        <v>525</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5006,11 +5006,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J67">
-        <v>525</v>
+        <v>699</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J68">
-        <v>699</v>
+        <v>670</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5156,11 +5156,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J69">
-        <v>670</v>
+        <v>1236</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5231,11 +5231,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J70">
-        <v>1236</v>
+        <v>1874</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5306,11 +5306,11 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J71">
-        <v>1874</v>
+        <v>820</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5381,11 +5381,11 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J72">
-        <v>820</v>
+        <v>291</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 25</t>
+          <t xml:space="preserve">Stadionvej 31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,16 +5451,16 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">751387, 3357680</t>
+          <t xml:space="preserve">751470, 3357680</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J73">
-        <v>291</v>
+        <v>169</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 31</t>
+          <t xml:space="preserve">Stadionvej 33</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,16 +5526,16 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">751470, 3357680</t>
+          <t xml:space="preserve">10067708, 100832613</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J74">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 33</t>
+          <t xml:space="preserve">Sverigesvej 1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,16 +5601,16 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067708, 100832613</t>
+          <t xml:space="preserve">8147317</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>100</v>
+        <v>448</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,17 +5666,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverigesvej 1</t>
+          <t xml:space="preserve">Søagervej 2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8147317</t>
+          <t xml:space="preserve">7009383</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="J76">
-        <v>448</v>
+        <v>170</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søagervej 2</t>
+          <t xml:space="preserve">Søagervej 4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7009383</t>
+          <t xml:space="preserve">8178401</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="J77">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søagervej 4</t>
+          <t xml:space="preserve">Sønder Alle 11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8178401</t>
+          <t xml:space="preserve">8647771, 100779577</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="J78">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Alle 11</t>
+          <t xml:space="preserve">Søndre Kajgade 10A</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,16 +5901,16 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8647771, 100779577</t>
+          <t xml:space="preserve">8647765</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J79">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Kajgade 10A</t>
+          <t xml:space="preserve">Søndre Kajgade 14A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,16 +5976,16 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8647765</t>
+          <t xml:space="preserve">751509, 8647765</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J80">
-        <v>70</v>
+        <v>964</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6041,26 +6041,26 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Kajgade 14A</t>
+          <t xml:space="preserve">Tempovej 9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">751509, 8647765</t>
+          <t xml:space="preserve">3356661</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J81">
-        <v>964</v>
+        <v>113</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6131,11 +6131,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J82">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6206,11 +6206,11 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J83">
-        <v>160</v>
+        <v>232</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6266,26 +6266,26 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempovej 9</t>
+          <t xml:space="preserve">Thoruphedevej 3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356661</t>
+          <t xml:space="preserve">7567144</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J84">
-        <v>232</v>
+        <v>781</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoruphedevej 3</t>
+          <t xml:space="preserve">Thygeslundvej 9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7567144</t>
+          <t xml:space="preserve">751464, 3354738</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="J85">
-        <v>781</v>
+        <v>361</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6416,26 +6416,26 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thygeslundvej 9</t>
+          <t xml:space="preserve">Tistedvej 3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">751464, 3354738</t>
+          <t xml:space="preserve">3345531</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J86">
-        <v>361</v>
+        <v>78</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6491,26 +6491,26 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tistedvej 3</t>
+          <t xml:space="preserve">Tobberupvej 8</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3345531</t>
+          <t xml:space="preserve">8925025</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J87">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J88">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobberupvej 8</t>
+          <t xml:space="preserve">Ulstrupvej 3A</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,16 +6651,16 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925025</t>
+          <t xml:space="preserve">3351970</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J89">
-        <v>420</v>
+        <v>687</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulstrupvej 3A</t>
+          <t xml:space="preserve">Ndr Truevej 8A</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351970</t>
+          <t xml:space="preserve">3352647</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J90">
-        <v>687</v>
+        <v>84</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014489</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6791,40 +6791,40 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr Truevej 8A</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3352647</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J91">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014489</t>
+          <t xml:space="preserve">200019779</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-03</t>
+          <t xml:space="preserve">2019-09-01</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,30 +6866,30 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Rosengade 15</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">5605526</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J92">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019779</t>
+          <t xml:space="preserve">100147933</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-01</t>
+          <t xml:space="preserve">2020-01-29</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,30 +6941,30 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosengade 15</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605526</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J93">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">100147933</t>
+          <t xml:space="preserve">200028021</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-29</t>
+          <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7031,11 +7031,11 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J94">
-        <v>170</v>
+        <v>239</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J95">
-        <v>239</v>
+        <v>141</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7166,40 +7166,40 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Langerimsvej 3B</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">751602, 3344137</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J96">
-        <v>141</v>
+        <v>490</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028021</t>
+          <t xml:space="preserve">100157186</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-12</t>
+          <t xml:space="preserve">2020-04-26</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J97">
-        <v>490</v>
+        <v>171</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7316,40 +7316,40 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langerimsvej 3B</t>
+          <t xml:space="preserve">Rostrup Skolevej 2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">751602, 3344137</t>
+          <t xml:space="preserve">751289, 3348300</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J98">
-        <v>171</v>
+        <v>243</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">100157186</t>
+          <t xml:space="preserve">200039279</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-26</t>
+          <t xml:space="preserve">2020-10-18</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rostrup Skolevej 2</t>
+          <t xml:space="preserve">Bønfeltvej 2D</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,30 +7401,30 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">751289, 3348300</t>
+          <t xml:space="preserve">3344709, 100801117</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>243</v>
+        <v>377</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039279</t>
+          <t xml:space="preserve">200039964</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-18</t>
+          <t xml:space="preserve">2020-10-28</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,17 +7466,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bønfeltvej 2D</t>
+          <t xml:space="preserve">Kjellerupsgade 18</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3344709, 100801117</t>
+          <t xml:space="preserve">751340, 3354159</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="J100">
-        <v>377</v>
+        <v>212</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039964</t>
+          <t xml:space="preserve">200040438</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-28</t>
+          <t xml:space="preserve">2020-11-05</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjellerupsgade 18</t>
+          <t xml:space="preserve">Thygeslundvej 9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">751340, 3354159</t>
+          <t xml:space="preserve">751464, 3354738</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7560,11 +7560,11 @@
         </is>
       </c>
       <c r="J101">
-        <v>212</v>
+        <v>872</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040438</t>
+          <t xml:space="preserve">200040715</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-05</t>
+          <t xml:space="preserve">2020-11-09</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,17 +7616,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thygeslundvej 9</t>
+          <t xml:space="preserve">Klejtrupvej 68A</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">751464, 3354738</t>
+          <t xml:space="preserve">751528, 4079467</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7635,11 +7635,11 @@
         </is>
       </c>
       <c r="J102">
-        <v>872</v>
+        <v>122</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040715</t>
+          <t xml:space="preserve">200040962</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-09</t>
+          <t xml:space="preserve">2020-11-12</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,17 +7691,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klejtrupvej 68A</t>
+          <t xml:space="preserve">Fjordgade 11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">751528, 4079467</t>
+          <t xml:space="preserve">751547, 7948895</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J103">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040962</t>
+          <t xml:space="preserve">200041424</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-12</t>
+          <t xml:space="preserve">2020-11-19</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 11</t>
+          <t xml:space="preserve">Fjordparken 2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">751547, 7948895</t>
+          <t xml:space="preserve">751551, 5606122</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,16 +7785,16 @@
         </is>
       </c>
       <c r="J104">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041424</t>
+          <t xml:space="preserve">200041425</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordparken 2</t>
+          <t xml:space="preserve">Klostermarken 15</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">751551, 5606122</t>
+          <t xml:space="preserve">10149847</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,21 +7860,21 @@
         </is>
       </c>
       <c r="J105">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041425</t>
+          <t xml:space="preserve">200041583</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-19</t>
+          <t xml:space="preserve">2020-11-23</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermarken 15</t>
+          <t xml:space="preserve">Skrødstrupvej 6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">10149847</t>
+          <t xml:space="preserve">751548, 4079273</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041583</t>
+          <t xml:space="preserve">200041947</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-23</t>
+          <t xml:space="preserve">2020-11-29</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrødstrupvej 6</t>
+          <t xml:space="preserve">Hjulhusvej 1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">751548, 4079273</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="J107">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041947</t>
+          <t xml:space="preserve">200042102</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-29</t>
+          <t xml:space="preserve">2020-12-01</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 1</t>
+          <t xml:space="preserve">Hjulhusvej 5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8081,15 +8081,15 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J108">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042102</t>
+          <t xml:space="preserve">200042106</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,40 +8141,40 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 5</t>
+          <t xml:space="preserve">Markedsgade 34</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">751482, 3355976</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>262</v>
+        <v>161</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042106</t>
+          <t xml:space="preserve">200042683</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-01</t>
+          <t xml:space="preserve">2020-12-09</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markedsgade 34</t>
+          <t xml:space="preserve">Sportsvej 5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">751482, 3355976</t>
+          <t xml:space="preserve">751472, 3355221</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042683</t>
+          <t xml:space="preserve">200042681</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 5</t>
+          <t xml:space="preserve">Vikingvej 10</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">751472, 3355221</t>
+          <t xml:space="preserve">751475, 3339528</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042681</t>
+          <t xml:space="preserve">200043700</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-09</t>
+          <t xml:space="preserve">2020-12-29</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 10</t>
+          <t xml:space="preserve">Ålborgvej 64</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,25 +8376,25 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">751475, 3339528</t>
+          <t xml:space="preserve">751480, 3357700</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J112">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043700</t>
+          <t xml:space="preserve">200043698</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8441,40 +8441,40 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 64</t>
+          <t xml:space="preserve">Fjordgade 16A</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">751480, 3357700</t>
+          <t xml:space="preserve">9738005</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043698</t>
+          <t xml:space="preserve">200046961</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-29</t>
+          <t xml:space="preserve">2021-03-18</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 16A</t>
+          <t xml:space="preserve">Stadionvej 33</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9738005</t>
+          <t xml:space="preserve">10067708, 100832613</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046961</t>
+          <t xml:space="preserve">200048874</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-18</t>
+          <t xml:space="preserve">2021-05-06</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8606,15 +8606,15 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J115">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048874</t>
+          <t xml:space="preserve">200048873</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 33</t>
+          <t xml:space="preserve">Idrætsvej 15</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,30 +8676,30 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067708, 100832613</t>
+          <t xml:space="preserve">751447, 3348690</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
-        <v>63</v>
+        <v>738</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048873</t>
+          <t xml:space="preserve">200059298</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve">Dansk Bygningstermografi</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-06</t>
+          <t xml:space="preserve">2022-05-03</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 15</t>
+          <t xml:space="preserve">Langerimsvej 7</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">751447, 3348690</t>
+          <t xml:space="preserve">751474, 3344194</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>738</v>
+        <v>1948</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059298</t>
+          <t xml:space="preserve">200059329</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-03</t>
+          <t xml:space="preserve">2022-05-06</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langerimsvej 7</t>
+          <t xml:space="preserve">Stadionvej 25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">751474, 3344194</t>
+          <t xml:space="preserve">751387, 3357680</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J118">
-        <v>1948</v>
+        <v>1398</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059329</t>
+          <t xml:space="preserve">200059504</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-06</t>
+          <t xml:space="preserve">2022-05-12</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8906,11 +8906,11 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J119">
-        <v>1398</v>
+        <v>253</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -8966,30 +8966,30 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 25</t>
+          <t xml:space="preserve">Døstrupvej 23</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">751387, 3357680</t>
+          <t xml:space="preserve">751529, 3346372</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J120">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059504</t>
+          <t xml:space="preserve">200060053</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-12</t>
+          <t xml:space="preserve">2022-06-08</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 23</t>
+          <t xml:space="preserve">Skolemarken 2A</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">751529, 3346372</t>
+          <t xml:space="preserve">751290, 8764792</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>216</v>
+        <v>898</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060053</t>
+          <t xml:space="preserve">200060070</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-08</t>
+          <t xml:space="preserve">2022-06-09</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,30 +9116,30 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolemarken 2A</t>
+          <t xml:space="preserve">Hvarrevej 6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">751290, 8764792</t>
+          <t xml:space="preserve">751283, 3351340</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J122">
-        <v>898</v>
+        <v>2188</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060070</t>
+          <t xml:space="preserve">200060601</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-09</t>
+          <t xml:space="preserve">2022-06-30</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 6</t>
+          <t xml:space="preserve">Hvarrevej 8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,20 +9201,20 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">751283, 3351340</t>
+          <t xml:space="preserve">751284, 3351342</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J123">
-        <v>2188</v>
+        <v>1371</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060601</t>
+          <t xml:space="preserve">200060602</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,40 +9266,40 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 8</t>
+          <t xml:space="preserve">Kirketoften 6A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">751284, 3351342</t>
+          <t xml:space="preserve">405503, 405504</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>1371</v>
+        <v>2595</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060602</t>
+          <t xml:space="preserve">311178903</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningstermografi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-30</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,30 +9341,30 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 6A</t>
+          <t xml:space="preserve">Kirkevej 13</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">405503, 405504</t>
+          <t xml:space="preserve">7864866</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J125">
-        <v>2595</v>
+        <v>360</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178903</t>
+          <t xml:space="preserve">311181429</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-07</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 13</t>
+          <t xml:space="preserve">Kirkevej 23</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J126">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 23</t>
+          <t xml:space="preserve">Kirkevej 9</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9506,15 +9506,15 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>360</v>
+        <v>2671</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181429</t>
+          <t xml:space="preserve">311181419</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 9</t>
+          <t xml:space="preserve">Kærvej 30</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7864866</t>
+          <t xml:space="preserve">8043516</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>2671</v>
+        <v>223</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181419</t>
+          <t xml:space="preserve">311184922</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-07</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9656,15 +9656,15 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J129">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184922</t>
+          <t xml:space="preserve">311184913</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9731,15 +9731,15 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J130">
-        <v>220</v>
+        <v>1366</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184913</t>
+          <t xml:space="preserve">311184922</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 30</t>
+          <t xml:space="preserve">Døstrupvej 1</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,20 +9801,20 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8043516</t>
+          <t xml:space="preserve">3346368</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J131">
-        <v>1366</v>
+        <v>506</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184922</t>
+          <t xml:space="preserve">311189004</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9881,15 +9881,15 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J132">
-        <v>506</v>
+        <v>824</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189004</t>
+          <t xml:space="preserve">311189007</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 1</t>
+          <t xml:space="preserve">Døstrupvej 3</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9956,15 +9956,15 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J133">
-        <v>824</v>
+        <v>228</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189007</t>
+          <t xml:space="preserve">311189034</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3</t>
+          <t xml:space="preserve">Døstrupvej 3A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,20 +10026,20 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346368</t>
+          <t xml:space="preserve">751530, 3346372</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J134">
-        <v>228</v>
+        <v>1064</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189034</t>
+          <t xml:space="preserve">311189044</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10106,11 +10106,11 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J135">
-        <v>1064</v>
+        <v>667</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10166,30 +10166,30 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 3A</t>
+          <t xml:space="preserve">Vikingvej 2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">751530, 3346372</t>
+          <t xml:space="preserve">3339443</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>667</v>
+        <v>206</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189044</t>
+          <t xml:space="preserve">311190150</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-08</t>
+          <t xml:space="preserve">2026-07-14</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 2</t>
+          <t xml:space="preserve">Vikingvej 4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10256,11 +10256,11 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J137">
-        <v>206</v>
+        <v>5980</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10316,40 +10316,40 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingvej 4</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339443</t>
+          <t xml:space="preserve">4078677</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J138">
-        <v>5980</v>
+        <v>1337</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190150</t>
+          <t xml:space="preserve">311190370</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-14</t>
+          <t xml:space="preserve">2026-07-15</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10406,11 +10406,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J139">
-        <v>1337</v>
+        <v>400</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J140">
-        <v>400</v>
+        <v>954</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J141">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10616,40 +10616,40 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Korsbakken 9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078677</t>
+          <t xml:space="preserve">3339512</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>957</v>
+        <v>442</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311190370</t>
+          <t xml:space="preserve">311200372</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-15</t>
+          <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsbakken 9</t>
+          <t xml:space="preserve">Savværksvej 5</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3339512</t>
+          <t xml:space="preserve">403587, 403588</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,11 +10710,11 @@
         </is>
       </c>
       <c r="J143">
-        <v>442</v>
+        <v>750</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200372</t>
+          <t xml:space="preserve">311202307</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14</t>
+          <t xml:space="preserve">2026-09-23</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Savværksvej 5</t>
+          <t xml:space="preserve">H I Biesgade 4</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,30 +10776,30 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">403587, 403588</t>
+          <t xml:space="preserve">5601067</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J144">
-        <v>750</v>
+        <v>287</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202307</t>
+          <t xml:space="preserve">311203630</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">H I Biesgade 4</t>
+          <t xml:space="preserve">Skolekrogen 2A</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,30 +10851,30 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601067</t>
+          <t xml:space="preserve">3351970</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>287</v>
+        <v>3982</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203630</t>
+          <t xml:space="preserve">311206964</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 2</t>
+          <t xml:space="preserve">Nyvangsvej 8</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351204</t>
+          <t xml:space="preserve">3356564</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>497</v>
+        <v>403</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206994</t>
+          <t xml:space="preserve">311207916</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolekrogen 2A</t>
+          <t xml:space="preserve">Søtofte 2A</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351970</t>
+          <t xml:space="preserve">4080676</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>3982</v>
+        <v>195</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206964</t>
+          <t xml:space="preserve">311207894</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangsvej 8</t>
+          <t xml:space="preserve">Daniavej 40</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356564</t>
+          <t xml:space="preserve">4078307</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>403</v>
+        <v>277</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207916</t>
+          <t xml:space="preserve">311212626</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søtofte 2A</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4080676</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>195</v>
+        <v>543</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207894</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,30 +11216,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniavej 40</t>
+          <t xml:space="preserve">Østergade 22</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078307</t>
+          <t xml:space="preserve">3351066</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J150">
-        <v>277</v>
+        <v>418</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212626</t>
+          <t xml:space="preserve">311241600</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11306,11 +11306,11 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J151">
-        <v>543</v>
+        <v>663</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Bluhmesgade 19</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,20 +11376,20 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">3350443</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>418</v>
+        <v>1768</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311246240</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,30 +11441,30 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 22</t>
+          <t xml:space="preserve">Digtervænget 46</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351066</t>
+          <t xml:space="preserve">5607088</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>663</v>
+        <v>538</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241600</t>
+          <t xml:space="preserve">311248868</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,17 +11516,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bluhmesgade 19</t>
+          <t xml:space="preserve">Gl Hobrovej 3A</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3350443</t>
+          <t xml:space="preserve">8038852</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,11 +11535,11 @@
         </is>
       </c>
       <c r="J154">
-        <v>1768</v>
+        <v>520</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246240</t>
+          <t xml:space="preserve">311248873</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digtervænget 46</t>
+          <t xml:space="preserve">Korsgade 2</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5607088</t>
+          <t xml:space="preserve">5600985</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>538</v>
+        <v>2360</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248868</t>
+          <t xml:space="preserve">311248882</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11666,17 +11666,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Hobrovej 3A</t>
+          <t xml:space="preserve">Nordre Kajgade 1</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038852</t>
+          <t xml:space="preserve">5600836</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>520</v>
+        <v>850</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248873</t>
+          <t xml:space="preserve">311248866</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,17 +11741,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgade 2</t>
+          <t xml:space="preserve">Rosendals Alle 8</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600985</t>
+          <t xml:space="preserve">3356457</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>2360</v>
+        <v>733</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248882</t>
+          <t xml:space="preserve">311256463</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,30 +11816,30 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 1</t>
+          <t xml:space="preserve">Rosendals Alle 8</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600836</t>
+          <t xml:space="preserve">3356457</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J158">
-        <v>850</v>
+        <v>237</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248866</t>
+          <t xml:space="preserve">311256464</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosendals Alle 8</t>
+          <t xml:space="preserve">Skolegade 12</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356457</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J159">
-        <v>733</v>
+        <v>666</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256463</t>
+          <t xml:space="preserve">311258677</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,40 +11966,40 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosendals Alle 8</t>
+          <t xml:space="preserve">Rørholmsgade 8</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356457</t>
+          <t xml:space="preserve">5601048</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J160">
-        <v>237</v>
+        <v>488</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256464</t>
+          <t xml:space="preserve">311259494</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12</t>
+          <t xml:space="preserve">Fjordgade 12</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,20 +12051,20 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">5601049</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J161">
-        <v>666</v>
+        <v>512</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258677</t>
+          <t xml:space="preserve">311261189</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,17 +12116,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørholmsgade 8</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601048</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,21 +12135,21 @@
         </is>
       </c>
       <c r="J162">
-        <v>488</v>
+        <v>1986</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259494</t>
+          <t xml:space="preserve">311261205</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2027-07-17</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,30 +12191,30 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 12</t>
+          <t xml:space="preserve">Hadsundvej 11</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601049</t>
+          <t xml:space="preserve">1801867</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J163">
-        <v>512</v>
+        <v>444</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261189</t>
+          <t xml:space="preserve">311261207</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Sjællandsvej 15</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5601328</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>1986</v>
+        <v>1380</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261205</t>
+          <t xml:space="preserve">311261221</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,30 +12341,30 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hadsundvej 11</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801867</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>444</v>
+        <v>556</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261207</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjællandsvej 15</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601328</t>
+          <t xml:space="preserve">5600594</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J166">
-        <v>1380</v>
+        <v>906</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261221</t>
+          <t xml:space="preserve">311261185</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,17 +12491,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Teglgade 6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5605653</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>556</v>
+        <v>621</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311261137</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600594</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>906</v>
+        <v>1994</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261185</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,30 +12641,30 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgade 6</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605653</t>
+          <t xml:space="preserve">5600589</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J169">
-        <v>621</v>
+        <v>757</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311261137</t>
+          <t xml:space="preserve">311267936</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-17</t>
+          <t xml:space="preserve">2027-08-23</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12731,11 +12731,11 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J170">
-        <v>1994</v>
+        <v>1368</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12806,11 +12806,11 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J171">
-        <v>757</v>
+        <v>2016</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12881,11 +12881,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J172">
-        <v>1368</v>
+        <v>540</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12956,11 +12956,11 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J173">
-        <v>2016</v>
+        <v>1876</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J174">
-        <v>540</v>
+        <v>834</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolebakken 41</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600589</t>
+          <t xml:space="preserve">7007296</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J175">
-        <v>1876</v>
+        <v>1326</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267936</t>
+          <t xml:space="preserve">311280820</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-23</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 19</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J176">
-        <v>834</v>
+        <v>1670</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286484</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 41</t>
+          <t xml:space="preserve">Amerikavej 21</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007296</t>
+          <t xml:space="preserve">5603041</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J177">
-        <v>1326</v>
+        <v>2252</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280820</t>
+          <t xml:space="preserve">311286483</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2027-11-30</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 19</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,20 +13326,20 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J178">
-        <v>1670</v>
+        <v>401</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286484</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21</t>
+          <t xml:space="preserve">Amerikavej 21B</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5603041</t>
+          <t xml:space="preserve">8225856</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J179">
-        <v>2252</v>
+        <v>401</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286483</t>
+          <t xml:space="preserve">311286480</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J180">
@@ -13556,11 +13556,11 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J181">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -13631,11 +13631,11 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J182">
-        <v>401</v>
+        <v>640</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -13706,11 +13706,11 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J183">
-        <v>448</v>
+        <v>354</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13781,15 +13781,15 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J184">
-        <v>640</v>
+        <v>296</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311286481</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13841,30 +13841,30 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Stadionvej 5</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">8379978</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J185">
-        <v>354</v>
+        <v>11962</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286480</t>
+          <t xml:space="preserve">311288954</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amerikavej 21B</t>
+          <t xml:space="preserve">Fayesgade 14A</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,20 +13926,20 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225856</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>296</v>
+        <v>1500</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286481</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-30</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,30 +13991,30 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 5</t>
+          <t xml:space="preserve">Fayesgade 14B</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">8379978</t>
+          <t xml:space="preserve">5602954</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J187">
-        <v>11962</v>
+        <v>2442</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288954</t>
+          <t xml:space="preserve">311289680</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-20</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14A</t>
+          <t xml:space="preserve">Fayesgade 14D</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14081,11 +14081,11 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J188">
-        <v>1500</v>
+        <v>740</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -14141,30 +14141,30 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14B</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J189">
-        <v>2442</v>
+        <v>1229</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,30 +14216,30 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fayesgade 14D</t>
+          <t xml:space="preserve">Hjulhusvej 3</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602954</t>
+          <t xml:space="preserve">5606443</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J190">
-        <v>740</v>
+        <v>1980</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289680</t>
+          <t xml:space="preserve">311290319</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-20</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14306,11 +14306,11 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J191">
-        <v>1229</v>
+        <v>1065</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14381,11 +14381,11 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J192">
-        <v>1980</v>
+        <v>535</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -14456,11 +14456,11 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J193">
-        <v>1065</v>
+        <v>535</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14531,11 +14531,11 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J194">
-        <v>535</v>
+        <v>377</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14591,30 +14591,30 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Ålborgvej 17A</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3357310</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J195">
-        <v>535</v>
+        <v>309</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311301379</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-07</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,30 +14666,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulhusvej 3</t>
+          <t xml:space="preserve">Tempovej 1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5606443</t>
+          <t xml:space="preserve">3356517</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J196">
-        <v>377</v>
+        <v>3384</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290319</t>
+          <t xml:space="preserve">311303211</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2028-03-16</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,17 +14741,17 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 17A</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357310</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -14760,11 +14760,11 @@
         </is>
       </c>
       <c r="J197">
-        <v>309</v>
+        <v>777</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301379</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-07</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,30 +14816,30 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempovej 1</t>
+          <t xml:space="preserve">Hvarrevej 10</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356517</t>
+          <t xml:space="preserve">3351341</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J198">
-        <v>3384</v>
+        <v>689</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311303211</t>
+          <t xml:space="preserve">311307573</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-16</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Sverigesvej 3</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">8516334</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,11 +14910,11 @@
         </is>
       </c>
       <c r="J199">
-        <v>777</v>
+        <v>2329</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311307590</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,30 +14966,30 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 10</t>
+          <t xml:space="preserve">Vinkelvej 3</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351341</t>
+          <t xml:space="preserve">3356821</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J200">
-        <v>689</v>
+        <v>69</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307573</t>
+          <t xml:space="preserve">311311580</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-05-02</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverigesvej 3</t>
+          <t xml:space="preserve">Timandsvej 25A</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">8516334</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15060,11 +15060,11 @@
         </is>
       </c>
       <c r="J201">
-        <v>2329</v>
+        <v>3913</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307590</t>
+          <t xml:space="preserve">311317939</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 3</t>
+          <t xml:space="preserve">Timandsvej 25D</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,20 +15126,20 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356821</t>
+          <t xml:space="preserve">3355834</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J202">
-        <v>69</v>
+        <v>546</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311311580</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-02</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25A</t>
+          <t xml:space="preserve">Timandsvej 25E</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15206,15 +15206,15 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J203">
-        <v>3913</v>
+        <v>546</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317939</t>
+          <t xml:space="preserve">311317937</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15266,30 +15266,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25D</t>
+          <t xml:space="preserve">Thoruphedevej 3</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7567144</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204">
-        <v>546</v>
+        <v>297</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311319914</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-12</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,30 +15341,30 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timandsvej 25E</t>
+          <t xml:space="preserve">Oxendalen 15B</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355834</t>
+          <t xml:space="preserve">7996792</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J205">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317937</t>
+          <t xml:space="preserve">311320212</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2028-06-13</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoruphedevej 3</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7567144</t>
+          <t xml:space="preserve">403144</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -15435,11 +15435,11 @@
         </is>
       </c>
       <c r="J206">
-        <v>297</v>
+        <v>2635</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319914</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-12</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,30 +15491,30 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15B</t>
+          <t xml:space="preserve">Myhlenbergvej 16</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">7996792</t>
+          <t xml:space="preserve">403144, 403145</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J207">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320212</t>
+          <t xml:space="preserve">311320908</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-13</t>
+          <t xml:space="preserve">2028-06-15</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15576,16 +15576,16 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144</t>
+          <t xml:space="preserve">403145</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J208">
-        <v>2635</v>
+        <v>462</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Myhlenbergvej 16A</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,20 +15651,20 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">403144, 403145</t>
+          <t xml:space="preserve">751286</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J209">
-        <v>612</v>
+        <v>150</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321692</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-20</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,20 +15726,20 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">403145</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J210">
-        <v>462</v>
+        <v>5917</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311320908</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-15</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Myhlenbergvej 16A</t>
+          <t xml:space="preserve">Storardenvej 22</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,20 +15801,20 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">751286</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J211">
-        <v>150</v>
+        <v>1420</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321692</t>
+          <t xml:space="preserve">311321991</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-20</t>
+          <t xml:space="preserve">2028-06-21</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Rugmarken 5</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">10050818</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,11 +15885,11 @@
         </is>
       </c>
       <c r="J212">
-        <v>5917</v>
+        <v>960</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311323471</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,30 +15941,30 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storardenvej 22</t>
+          <t xml:space="preserve">Bernadottegården 60</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J213">
-        <v>1420</v>
+        <v>189</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311321991</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-21</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,30 +16016,30 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rugmarken 5</t>
+          <t xml:space="preserve">Bernadottegården 61</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050818</t>
+          <t xml:space="preserve">3356704</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J214">
-        <v>960</v>
+        <v>189</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323471</t>
+          <t xml:space="preserve">311324162</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-28</t>
+          <t xml:space="preserve">2028-07-02</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 60</t>
+          <t xml:space="preserve">Bernadottegården 66</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J215">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 61</t>
+          <t xml:space="preserve">Bernadottegården 67</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J216">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 66</t>
+          <t xml:space="preserve">Bernadottegården 72</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16256,11 +16256,11 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J217">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 67</t>
+          <t xml:space="preserve">Bernadottegården 75</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J218">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 72</t>
+          <t xml:space="preserve">Bernadottegården 80</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J219">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 75</t>
+          <t xml:space="preserve">Bernadottegården 83</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J220">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 80</t>
+          <t xml:space="preserve">Bernadottegården 88</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16556,11 +16556,11 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J221">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 83</t>
+          <t xml:space="preserve">Bernadottegården 94</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16631,15 +16631,15 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J222">
-        <v>252</v>
+        <v>5059</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311324163</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16691,40 +16691,40 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 88</t>
+          <t xml:space="preserve">Edderupvej 3</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">4078847</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J223">
-        <v>189</v>
+        <v>802</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324162</t>
+          <t xml:space="preserve">311329619</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,17 +16766,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernadottegården 94</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356704</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -16785,11 +16785,11 @@
         </is>
       </c>
       <c r="J224">
-        <v>5059</v>
+        <v>709</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324163</t>
+          <t xml:space="preserve">311340955</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-02</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edderupvej 3</t>
+          <t xml:space="preserve">Oxendalen 15</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16851,30 +16851,30 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078847</t>
+          <t xml:space="preserve">5605845</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J225">
-        <v>802</v>
+        <v>450</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329619</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-09</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16931,15 +16931,15 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J226">
-        <v>709</v>
+        <v>450</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340955</t>
+          <t xml:space="preserve">311340956</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J227">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J228">
@@ -17141,40 +17141,40 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Skolebakken 4B</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">8990</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">751527, 4089217</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J229">
-        <v>450</v>
+        <v>268</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311382849</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2029-06-17</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,40 +17216,40 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oxendalen 15</t>
+          <t xml:space="preserve">Tobberupvej 8</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605845</t>
+          <t xml:space="preserve">8925025</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J230">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340956</t>
+          <t xml:space="preserve">311499497</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA Rådgivning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,40 +17291,40 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 4B</t>
+          <t xml:space="preserve">Solvej 10</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">8990</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">751527, 4089217</t>
+          <t xml:space="preserve">1808922</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J231">
-        <v>268</v>
+        <v>1431</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311382849</t>
+          <t xml:space="preserve">311574350</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">Hus Check ApS</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-17</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobberupvej 8</t>
+          <t xml:space="preserve">Skivevej 27</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17376,30 +17376,30 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925025</t>
+          <t xml:space="preserve">405931, 100798376</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J232">
-        <v>350</v>
+        <v>293</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311499497</t>
+          <t xml:space="preserve">311609330</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-01</t>
+          <t xml:space="preserve">2032-06-21</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,40 +17441,40 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvej 10</t>
+          <t xml:space="preserve">Østergade 21</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808922</t>
+          <t xml:space="preserve">403157, 403158</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J233">
-        <v>1431</v>
+        <v>501</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574350</t>
+          <t xml:space="preserve">311627846</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hus Check ApS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-09-14</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,30 +17516,30 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skivevej 27</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">405931, 100798376</t>
+          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J234">
-        <v>293</v>
+        <v>5995</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609330</t>
+          <t xml:space="preserve">311646437</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-21</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,17 +17591,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 21</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">403157, 403158</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -17610,21 +17610,21 @@
         </is>
       </c>
       <c r="J235">
-        <v>501</v>
+        <v>391</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311627846</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-14</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,40 +17666,40 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Søndre Ringvej 9</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">403107, 403110, 403108, 403109</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J236">
-        <v>5995</v>
+        <v>925</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646437</t>
+          <t xml:space="preserve">311657088</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-01-26</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17756,11 +17756,11 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J237">
-        <v>391</v>
+        <v>2948</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -17831,11 +17831,11 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J238">
-        <v>925</v>
+        <v>800</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -17906,11 +17906,11 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J239">
-        <v>2948</v>
+        <v>451</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -17981,11 +17981,11 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J240">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -18041,40 +18041,40 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Himmerlandsgade 9</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">8603975</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J241">
-        <v>451</v>
+        <v>3721</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311670894</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 9</t>
+          <t xml:space="preserve">Håndværkerparken 2</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18126,30 +18126,30 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">5602463</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J242">
-        <v>825</v>
+        <v>586</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657088</t>
+          <t xml:space="preserve">311688591</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">Ingeniørconsult aps</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-26</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,30 +18191,30 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmerlandsgade 9</t>
+          <t xml:space="preserve">Søndre Ringvej 11</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">8603975</t>
+          <t xml:space="preserve">5602642</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J243">
-        <v>3721</v>
+        <v>341</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670894</t>
+          <t xml:space="preserve">311688585</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-06-18</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Håndværkerparken 2</t>
+          <t xml:space="preserve">Kirkegårdsvej 3A</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602463</t>
+          <t xml:space="preserve">3346084</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -18285,21 +18285,21 @@
         </is>
       </c>
       <c r="J244">
-        <v>586</v>
+        <v>163</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688591</t>
+          <t xml:space="preserve">311733666</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-01-17</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Ringvej 11</t>
+          <t xml:space="preserve">Adelgade 30B</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,30 +18351,30 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602642</t>
+          <t xml:space="preserve">5601052</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
-        <v>341</v>
+        <v>638</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688585</t>
+          <t xml:space="preserve">311790164</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørconsult aps</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-18</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,17 +18416,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegårdsvej 3A</t>
+          <t xml:space="preserve">Plantagevej 1</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346084</t>
+          <t xml:space="preserve">8611069</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -18435,21 +18435,21 @@
         </is>
       </c>
       <c r="J246">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733666</t>
+          <t xml:space="preserve">311790167</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådg. Ingeniørfirma Søren Sørensen A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-17</t>
+          <t xml:space="preserve">2034-10-08</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,30 +18491,30 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30B</t>
+          <t xml:space="preserve">Plantagevej 10</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601052</t>
+          <t xml:space="preserve">8611069</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J247">
-        <v>638</v>
+        <v>67</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790164</t>
+          <t xml:space="preserve">311790167</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 1</t>
+          <t xml:space="preserve">Plantagevej 15A</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18581,7 +18581,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J248">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 10</t>
+          <t xml:space="preserve">Plantagevej 15C</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18656,7 +18656,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J249">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 15A</t>
+          <t xml:space="preserve">Plantagevej 15E</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J250">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 15C</t>
+          <t xml:space="preserve">Plantagevej 2</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J251">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 15E</t>
+          <t xml:space="preserve">Plantagevej 6</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J252">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 2</t>
+          <t xml:space="preserve">Plantagevej 9</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J253">
@@ -19016,30 +19016,30 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 6</t>
+          <t xml:space="preserve">Søndre Kajgade 18A</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">8611069</t>
+          <t xml:space="preserve">5600779, 100891198</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J254">
-        <v>67</v>
+        <v>1062</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790167</t>
+          <t xml:space="preserve">311790163</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 9</t>
+          <t xml:space="preserve">Finlandsvej 14</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19101,20 +19101,20 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">8611069</t>
+          <t xml:space="preserve">10067706</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J255">
-        <v>67</v>
+        <v>214</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790167</t>
+          <t xml:space="preserve">311829972</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2035-05-07</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Kajgade 18A</t>
+          <t xml:space="preserve">Nordre Kajgade 3A</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600779, 100891198</t>
+          <t xml:space="preserve">7006509</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -19185,11 +19185,11 @@
         </is>
       </c>
       <c r="J256">
-        <v>1062</v>
+        <v>225</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790163</t>
+          <t xml:space="preserve">311829971</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-08</t>
+          <t xml:space="preserve">2035-05-07</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,30 +19241,30 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finlandsvej 14</t>
+          <t xml:space="preserve">Houvej 4</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">10067706</t>
+          <t xml:space="preserve">7010134</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J257">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829972</t>
+          <t xml:space="preserve">311871711</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-07</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,30 +19316,30 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 3A</t>
+          <t xml:space="preserve">Hvarrevej 19</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">7006509</t>
+          <t xml:space="preserve">9024269</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J258">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829971</t>
+          <t xml:space="preserve">311871713</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-07</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,30 +19391,30 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houvej 4</t>
+          <t xml:space="preserve">Fjordgade 7</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010134</t>
+          <t xml:space="preserve">7440925, 100764817</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J259">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871711</t>
+          <t xml:space="preserve">311879402</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,30 +19466,30 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvarrevej 19</t>
+          <t xml:space="preserve">Dorrelundsvej 3</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">9510</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">9024269</t>
+          <t xml:space="preserve">4079414</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>315</v>
+        <v>60</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871713</t>
+          <t xml:space="preserve">311887002</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,40 +19541,40 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordgade 7</t>
+          <t xml:space="preserve">Havnen 42</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">7440925, 100764817</t>
+          <t xml:space="preserve">751454, 8603833</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J261">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879402</t>
+          <t xml:space="preserve">311887010</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-03-12</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,35 +19616,35 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dorrelundsvej 3</t>
+          <t xml:space="preserve">Havnen 43</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">4079414</t>
+          <t xml:space="preserve">8603833</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J262">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887002</t>
+          <t xml:space="preserve">311887010</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 42</t>
+          <t xml:space="preserve">Havnen 44</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19701,16 +19701,16 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">751454, 8603833</t>
+          <t xml:space="preserve">751468, 8603833</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J263">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -19766,35 +19766,35 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 43</t>
+          <t xml:space="preserve">Kirkegade 2</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">8603833</t>
+          <t xml:space="preserve">5605751</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J264">
-        <v>112</v>
+        <v>357</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887010</t>
+          <t xml:space="preserve">311887008</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 44</t>
+          <t xml:space="preserve">Stadionvej 9A</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,25 +19851,25 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">751468, 8603833</t>
+          <t xml:space="preserve">100024816</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J265">
-        <v>178</v>
+        <v>339</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887010</t>
+          <t xml:space="preserve">311887007</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 2</t>
+          <t xml:space="preserve">Storegade 52</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5605751</t>
+          <t xml:space="preserve">4078682</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -19935,11 +19935,11 @@
         </is>
       </c>
       <c r="J266">
-        <v>357</v>
+        <v>210</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887008</t>
+          <t xml:space="preserve">311887003</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9A</t>
+          <t xml:space="preserve">Gl Visborgvej 21</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">100024816</t>
+          <t xml:space="preserve">3356303</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -20010,11 +20010,11 @@
         </is>
       </c>
       <c r="J267">
-        <v>339</v>
+        <v>510</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887007</t>
+          <t xml:space="preserve">311891993</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-01</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,30 +20066,30 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 52</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4078682</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J268">
-        <v>210</v>
+        <v>468</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887003</t>
+          <t xml:space="preserve">311896233</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-12</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,30 +20141,30 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Visborgvej 21</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">3356303</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J269">
-        <v>510</v>
+        <v>235</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311891993</t>
+          <t xml:space="preserve">311896234</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-01</t>
+          <t xml:space="preserve">2036-04-23</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Døstrupvej 33A</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20231,15 +20231,15 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J270">
-        <v>468</v>
+        <v>659</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896233</t>
+          <t xml:space="preserve">311896228</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Døstrupvej 21</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20301,20 +20301,20 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">100036624</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J271">
-        <v>235</v>
+        <v>1670</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896234</t>
+          <t xml:space="preserve">311898865</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33A</t>
+          <t xml:space="preserve">Kirketoften 5</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20376,20 +20376,20 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">5602982</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J272">
-        <v>659</v>
+        <v>2050</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896228</t>
+          <t xml:space="preserve">311898863</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-23</t>
+          <t xml:space="preserve">2036-05-05</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,17 +20441,17 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 21</t>
+          <t xml:space="preserve">Vestergade 4</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">100036624</t>
+          <t xml:space="preserve">3355780</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -20460,11 +20460,11 @@
         </is>
       </c>
       <c r="J273">
-        <v>1670</v>
+        <v>2199</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898865</t>
+          <t xml:space="preserve">311899310</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-06</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 5</t>
+          <t xml:space="preserve">Christiansgade 10</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602982</t>
+          <t xml:space="preserve">5600572</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -20535,11 +20535,11 @@
         </is>
       </c>
       <c r="J274">
-        <v>2050</v>
+        <v>881</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898863</t>
+          <t xml:space="preserve">311903717</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-05</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,30 +20591,30 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 4</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">9560</t>
+          <t xml:space="preserve">9500</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">3355780</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J275">
-        <v>2199</v>
+        <v>786</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899310</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-06</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansgade 10</t>
+          <t xml:space="preserve">Døstrupvej 33</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20676,20 +20676,20 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600572</t>
+          <t xml:space="preserve">3346274</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J276">
-        <v>881</v>
+        <v>369</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903717</t>
+          <t xml:space="preserve">311903714</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20756,11 +20756,11 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J277">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -20831,11 +20831,11 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J278">
-        <v>369</v>
+        <v>2989</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -20906,11 +20906,11 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J279">
-        <v>770</v>
+        <v>139</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -20981,11 +20981,11 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J280">
-        <v>2989</v>
+        <v>1421</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -21056,11 +21056,11 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J281">
-        <v>139</v>
+        <v>479</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Gettrupvej 3</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -21126,20 +21126,20 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7007800</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J282">
-        <v>1421</v>
+        <v>1127</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918912</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Døstrupvej 33</t>
+          <t xml:space="preserve">Ulstrupvej 3C</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -21201,20 +21201,20 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">3346274</t>
+          <t xml:space="preserve">7934937</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J283">
-        <v>479</v>
+        <v>635</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903714</t>
+          <t xml:space="preserve">311918911</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gettrupvej 3</t>
+          <t xml:space="preserve">Adelgade 28A</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -21276,20 +21276,20 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007800</t>
+          <t xml:space="preserve">5600946</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J284">
-        <v>1127</v>
+        <v>1095</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918912</t>
+          <t xml:space="preserve">311925680</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulstrupvej 3C</t>
+          <t xml:space="preserve">Adelgade 30A</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">7934937</t>
+          <t xml:space="preserve">5601054</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -21360,11 +21360,11 @@
         </is>
       </c>
       <c r="J285">
-        <v>635</v>
+        <v>400</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918911</t>
+          <t xml:space="preserve">311925679</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21416,17 +21416,17 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 28A</t>
+          <t xml:space="preserve">Kønigsfeldtsvej 7</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600946</t>
+          <t xml:space="preserve">4077985</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -21435,11 +21435,11 @@
         </is>
       </c>
       <c r="J286">
-        <v>1095</v>
+        <v>2226</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925680</t>
+          <t xml:space="preserve">311926396</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-09-17</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21491,30 +21491,30 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 30A</t>
+          <t xml:space="preserve">Ringvejen 1</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">9500</t>
+          <t xml:space="preserve">9560</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601054</t>
+          <t xml:space="preserve">3356242</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J287">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925679</t>
+          <t xml:space="preserve">311930425</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,17 +21566,17 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kønigsfeldtsvej 7</t>
+          <t xml:space="preserve">Rugmarken 2</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9510</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">4077985</t>
+          <t xml:space="preserve">3351204</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -21585,11 +21585,11 @@
         </is>
       </c>
       <c r="J288">
-        <v>2226</v>
+        <v>497</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926396</t>
+          <t xml:space="preserve">311930424</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-17</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
